--- a/old/260808.xlsx
+++ b/old/260808.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eigen\Git\de-tic-tacX\old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C905E6A-DFDD-4C09-B8CE-61C88D04426A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F2FD656-6BD5-4B03-AA67-BC9949CFBFC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="290" yWindow="4110" windowWidth="15030" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10720" yWindow="4730" windowWidth="15010" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="3" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Hahne: Zu Gast im Deutschlandfunk Interview der Woche ist Bernhard Mattes, Vorsitzender der Geschäftsführung von Ford Deutschland.
 Herr Mattes, nicht nur das Auto wird sich in Zukunft verändern, sondern auch wie es gebaut wird, Stichwort """""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" Industrie 4.0"""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""""" , also die Vernetzung der gesamten Wertschöpfungskette.
@@ -548,23 +548,6 @@
     <t>In der Energiepolitik haben wir, Gott sei Dank, viel geschafft, sie ist endlich wieder planbar und berechenbar geworden.
 Aber dann bleibt es so wie heute, dass wir eine hohe Beschäftigtenzahl haben, dass wir endlich wieder steigende Löhne haben.
 Bekämpfung vielleicht auch von Fluchtursachen in Ländern wie Syrien oder in Afrika, wenn ich an weitere Stichworte, die auch immer in der Debatte fallen, wie mehr Geld für die Bundeswehr oder – wie Sie es gerade gesagt haben, Herr Gabriel – mehr Geld für soziale Sicherheit, für den sozialen Zusammenhalt im Land</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Kriegsverbrecherhandlungen</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Das sah ja </t>
-  </si>
-  <si>
-    <t>ein Projekt nach dem anderen</t>
-  </si>
-  <si>
-    <t>flachte dann etwas ab</t>
-  </si>
-  <si>
-    <t>Umfragewerten nie richtig niedergeschlagen. Woran liegt das?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -900,45 +883,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87F8398F-ACF3-42F9-9228-F1CBE1BEB6D7}">
-  <dimension ref="A1:A7"/>
+  <dimension ref="A6:A7"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="52.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-    </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
